--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1198,6 +1198,551 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121622328</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58224</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100141</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Triturus cristatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>666894</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6614616</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Vide Ohlin</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>ASC0019g Groddjursinventering Arlanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121622333</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58221</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>666896</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6614615</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>22:02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>22:02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Vide Ohlin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>ASC0019g Groddjursinventering Arlanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121622332</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58224</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100141</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Triturus cristatus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>666891</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6614631</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>22:06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>22:06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>satt med huvudet upp över ytan.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Vide Ohlin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>ASC0019g Groddjursinventering Arlanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121622334</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58224</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100141</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Större vattensalamander</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Triturus cristatus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>666894</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6614615</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>22:01</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>22:01</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Vide Ohlin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>ASC0019g Groddjursinventering Arlanda</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121622328</v>
+        <v>121622332</v>
       </c>
       <c r="B7" t="n">
         <v>58224</v>
@@ -1248,6 +1248,11 @@
           <t>hane</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1259,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>666894</v>
+        <v>666891</v>
       </c>
       <c r="R7" t="n">
-        <v>6614616</v>
+        <v>6614631</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1294,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1304,7 +1309,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>satt med huvudet upp över ytan.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,10 +1345,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121622333</v>
+        <v>121622334</v>
       </c>
       <c r="B8" t="n">
-        <v>58221</v>
+        <v>58224</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1351,26 +1361,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1378,6 +1388,11 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1389,7 +1404,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>666896</v>
+        <v>666894</v>
       </c>
       <c r="R8" t="n">
         <v>6614615</v>
@@ -1424,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1434,7 +1449,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1465,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121622332</v>
+        <v>121622333</v>
       </c>
       <c r="B9" t="n">
-        <v>58224</v>
+        <v>58221</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,26 +1496,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100141</v>
+        <v>208242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1508,16 +1523,6 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1529,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>666891</v>
+        <v>666896</v>
       </c>
       <c r="R9" t="n">
-        <v>6614631</v>
+        <v>6614615</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1564,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22:06</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1574,12 +1579,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>22:06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>satt med huvudet upp över ytan.</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,7 +1610,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121622334</v>
+        <v>121622328</v>
       </c>
       <c r="B10" t="n">
         <v>58224</v>
@@ -1672,7 +1672,7 @@
         <v>666894</v>
       </c>
       <c r="R10" t="n">
-        <v>6614615</v>
+        <v>6614616</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121622332</v>
+        <v>121622334</v>
       </c>
       <c r="B7" t="n">
-        <v>58224</v>
+        <v>58227</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1248,11 +1248,6 @@
           <t>hane</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1264,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>666891</v>
+        <v>666894</v>
       </c>
       <c r="R7" t="n">
-        <v>6614631</v>
+        <v>6614615</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1299,7 +1294,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>22:06</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,12 +1304,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>22:06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>satt med huvudet upp över ytan.</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121622334</v>
+        <v>121622328</v>
       </c>
       <c r="B8" t="n">
-        <v>58224</v>
+        <v>58227</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,7 +1397,7 @@
         <v>666894</v>
       </c>
       <c r="R8" t="n">
-        <v>6614615</v>
+        <v>6614616</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1439,7 +1429,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,7 +1439,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121622333</v>
+        <v>121622332</v>
       </c>
       <c r="B9" t="n">
-        <v>58221</v>
+        <v>58227</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,26 +1486,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1523,6 +1513,16 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1534,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>666896</v>
+        <v>666891</v>
       </c>
       <c r="R9" t="n">
-        <v>6614615</v>
+        <v>6614631</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1569,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,7 +1579,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>22:06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>satt med huvudet upp över ytan.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,7 +1615,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121622328</v>
+        <v>121622333</v>
       </c>
       <c r="B10" t="n">
         <v>58224</v>
@@ -1626,26 +1631,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100141</v>
+        <v>208242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1653,11 +1658,6 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>666894</v>
+        <v>666896</v>
       </c>
       <c r="R10" t="n">
-        <v>6614616</v>
+        <v>6614615</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121622328</v>
+        <v>121622333</v>
       </c>
       <c r="B7" t="n">
-        <v>58227</v>
+        <v>58224</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,26 +1216,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100141</v>
+        <v>208242</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1243,11 +1243,6 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1259,10 +1254,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>666894</v>
+        <v>666896</v>
       </c>
       <c r="R7" t="n">
-        <v>6614616</v>
+        <v>6614615</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1294,7 +1289,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1304,7 +1299,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,7 +1330,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121622334</v>
+        <v>121622328</v>
       </c>
       <c r="B8" t="n">
         <v>58227</v>
@@ -1397,7 +1392,7 @@
         <v>666894</v>
       </c>
       <c r="R8" t="n">
-        <v>6614615</v>
+        <v>6614616</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1429,7 +1424,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1434,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,10 +1465,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121622333</v>
+        <v>121622334</v>
       </c>
       <c r="B9" t="n">
-        <v>58224</v>
+        <v>58227</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,26 +1481,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1513,6 +1508,11 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1524,7 +1524,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>666896</v>
+        <v>666894</v>
       </c>
       <c r="R9" t="n">
         <v>6614615</v>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121622333</v>
+        <v>121622328</v>
       </c>
       <c r="B7" t="n">
-        <v>58224</v>
+        <v>58227</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,26 +1216,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1243,6 +1243,11 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1254,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>666896</v>
+        <v>666894</v>
       </c>
       <c r="R7" t="n">
-        <v>6614615</v>
+        <v>6614616</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1289,7 +1294,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1299,7 +1304,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1330,7 +1335,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121622328</v>
+        <v>121622332</v>
       </c>
       <c r="B8" t="n">
         <v>58227</v>
@@ -1378,6 +1383,11 @@
           <t>hane</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1389,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>666894</v>
+        <v>666891</v>
       </c>
       <c r="R8" t="n">
-        <v>6614616</v>
+        <v>6614631</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1424,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1434,7 +1444,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>satt med huvudet upp över ytan.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1600,10 +1615,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121622332</v>
+        <v>121622333</v>
       </c>
       <c r="B10" t="n">
-        <v>58227</v>
+        <v>58224</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,26 +1631,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100141</v>
+        <v>208242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1643,16 +1658,6 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1664,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>666891</v>
+        <v>666896</v>
       </c>
       <c r="R10" t="n">
-        <v>6614631</v>
+        <v>6614615</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1699,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>22:06</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1709,12 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>22:06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>satt med huvudet upp över ytan.</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121622328</v>
+        <v>121622332</v>
       </c>
       <c r="B7" t="n">
         <v>58227</v>
@@ -1248,6 +1248,11 @@
           <t>hane</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1259,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>666894</v>
+        <v>666891</v>
       </c>
       <c r="R7" t="n">
-        <v>6614616</v>
+        <v>6614631</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1294,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1304,7 +1309,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>satt med huvudet upp över ytan.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,7 +1345,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121622332</v>
+        <v>121622334</v>
       </c>
       <c r="B8" t="n">
         <v>58227</v>
@@ -1383,11 +1393,6 @@
           <t>hane</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1399,10 +1404,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>666891</v>
+        <v>666894</v>
       </c>
       <c r="R8" t="n">
-        <v>6614631</v>
+        <v>6614615</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1434,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>22:06</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,12 +1449,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>22:06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>satt med huvudet upp över ytan.</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121622334</v>
+        <v>121622333</v>
       </c>
       <c r="B9" t="n">
-        <v>58227</v>
+        <v>58224</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,26 +1496,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100141</v>
+        <v>208242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1523,11 +1523,6 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1539,7 +1534,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>666894</v>
+        <v>666896</v>
       </c>
       <c r="R9" t="n">
         <v>6614615</v>
@@ -1574,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1579,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1615,10 +1610,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121622333</v>
+        <v>121622328</v>
       </c>
       <c r="B10" t="n">
-        <v>58224</v>
+        <v>58227</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,26 +1626,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1658,6 +1653,11 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>666896</v>
+        <v>666894</v>
       </c>
       <c r="R10" t="n">
-        <v>6614615</v>
+        <v>6614616</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121622332</v>
+        <v>121622334</v>
       </c>
       <c r="B7" t="n">
         <v>58227</v>
@@ -1248,11 +1248,6 @@
           <t>hane</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1264,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>666891</v>
+        <v>666894</v>
       </c>
       <c r="R7" t="n">
-        <v>6614631</v>
+        <v>6614615</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1299,7 +1294,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>22:06</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,12 +1304,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>22:06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>satt med huvudet upp över ytan.</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1345,7 +1335,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121622334</v>
+        <v>121622332</v>
       </c>
       <c r="B8" t="n">
         <v>58227</v>
@@ -1393,6 +1383,11 @@
           <t>hane</t>
         </is>
       </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1404,10 +1399,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>666894</v>
+        <v>666891</v>
       </c>
       <c r="R8" t="n">
-        <v>6614615</v>
+        <v>6614631</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1439,7 +1434,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1449,7 +1444,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>22:06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>satt med huvudet upp över ytan.</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121622334</v>
+        <v>121622332</v>
       </c>
       <c r="B7" t="n">
         <v>58227</v>
@@ -1248,6 +1248,11 @@
           <t>hane</t>
         </is>
       </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1259,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>666894</v>
+        <v>666891</v>
       </c>
       <c r="R7" t="n">
-        <v>6614615</v>
+        <v>6614631</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1294,7 +1299,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1304,7 +1309,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>22:06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>satt med huvudet upp över ytan.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,7 +1345,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121622332</v>
+        <v>121622328</v>
       </c>
       <c r="B8" t="n">
         <v>58227</v>
@@ -1383,11 +1393,6 @@
           <t>hane</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1399,10 +1404,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>666891</v>
+        <v>666894</v>
       </c>
       <c r="R8" t="n">
-        <v>6614631</v>
+        <v>6614616</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1434,7 +1439,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>22:06</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1444,12 +1449,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>22:06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>satt med huvudet upp över ytan.</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1480,10 +1480,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121622333</v>
+        <v>121622334</v>
       </c>
       <c r="B9" t="n">
-        <v>58224</v>
+        <v>58227</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,26 +1496,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1523,6 +1523,11 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1534,7 +1539,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>666896</v>
+        <v>666894</v>
       </c>
       <c r="R9" t="n">
         <v>6614615</v>
@@ -1569,7 +1574,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,7 +1584,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,10 +1615,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121622328</v>
+        <v>121622333</v>
       </c>
       <c r="B10" t="n">
-        <v>58227</v>
+        <v>58224</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,26 +1631,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100141</v>
+        <v>208242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1653,11 +1658,6 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>666894</v>
+        <v>666896</v>
       </c>
       <c r="R10" t="n">
-        <v>6614616</v>
+        <v>6614615</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1704,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121622332</v>
+        <v>121622334</v>
       </c>
       <c r="B7" t="n">
         <v>58227</v>
@@ -1248,11 +1248,6 @@
           <t>hane</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1264,10 +1259,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>666891</v>
+        <v>666894</v>
       </c>
       <c r="R7" t="n">
-        <v>6614631</v>
+        <v>6614615</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1299,7 +1294,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>22:06</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1309,12 +1304,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>22:06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>satt med huvudet upp över ytan.</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1480,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121622334</v>
+        <v>121622333</v>
       </c>
       <c r="B9" t="n">
-        <v>58227</v>
+        <v>58224</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1496,26 +1486,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100141</v>
+        <v>208242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1523,11 +1513,6 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1539,7 +1524,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>666894</v>
+        <v>666896</v>
       </c>
       <c r="R9" t="n">
         <v>6614615</v>
@@ -1574,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1584,7 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1615,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121622333</v>
+        <v>121622332</v>
       </c>
       <c r="B10" t="n">
-        <v>58224</v>
+        <v>58227</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,26 +1616,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1658,6 +1643,16 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1669,10 +1664,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>666896</v>
+        <v>666891</v>
       </c>
       <c r="R10" t="n">
-        <v>6614615</v>
+        <v>6614631</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1704,7 +1699,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1709,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>22:06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>satt med huvudet upp över ytan.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -1203,7 +1203,7 @@
         <v>121622334</v>
       </c>
       <c r="B7" t="n">
-        <v>58227</v>
+        <v>58235</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>121622328</v>
       </c>
       <c r="B8" t="n">
-        <v>58227</v>
+        <v>58235</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1470,10 +1470,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121622333</v>
+        <v>121622332</v>
       </c>
       <c r="B9" t="n">
-        <v>58224</v>
+        <v>58235</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1486,26 +1486,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1513,6 +1513,16 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1524,10 +1534,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>666896</v>
+        <v>666891</v>
       </c>
       <c r="R9" t="n">
-        <v>6614615</v>
+        <v>6614631</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1559,7 +1569,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1569,7 +1579,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>22:06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>satt med huvudet upp över ytan.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,10 +1615,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121622332</v>
+        <v>121622333</v>
       </c>
       <c r="B10" t="n">
-        <v>58227</v>
+        <v>58232</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,26 +1631,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100141</v>
+        <v>208242</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1643,16 +1658,6 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1664,10 +1669,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>666891</v>
+        <v>666896</v>
       </c>
       <c r="R10" t="n">
-        <v>6614631</v>
+        <v>6614615</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1699,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>22:06</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1709,12 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>22:06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>satt med huvudet upp över ytan.</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121622334</v>
+        <v>121622333</v>
       </c>
       <c r="B7" t="n">
-        <v>58235</v>
+        <v>58232</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,26 +1216,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100141</v>
+        <v>208242</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1243,11 +1243,6 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1259,7 +1254,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>666894</v>
+        <v>666896</v>
       </c>
       <c r="R7" t="n">
         <v>6614615</v>
@@ -1294,7 +1289,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1304,7 +1299,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>22:01</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,7 +1330,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121622328</v>
+        <v>121622334</v>
       </c>
       <c r="B8" t="n">
         <v>58235</v>
@@ -1397,7 +1392,7 @@
         <v>666894</v>
       </c>
       <c r="R8" t="n">
-        <v>6614616</v>
+        <v>6614615</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1429,7 +1424,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1439,7 +1434,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1470,7 +1465,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121622332</v>
+        <v>121622328</v>
       </c>
       <c r="B9" t="n">
         <v>58235</v>
@@ -1518,11 +1513,6 @@
           <t>hane</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
       <c r="N9" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1534,10 +1524,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>666891</v>
+        <v>666894</v>
       </c>
       <c r="R9" t="n">
-        <v>6614631</v>
+        <v>6614616</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1569,7 +1559,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>22:06</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1579,12 +1569,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>22:06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>satt med huvudet upp över ytan.</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1615,10 +1600,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121622333</v>
+        <v>121622332</v>
       </c>
       <c r="B10" t="n">
-        <v>58232</v>
+        <v>58235</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,26 +1616,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1658,6 +1643,16 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1669,10 +1664,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>666896</v>
+        <v>666891</v>
       </c>
       <c r="R10" t="n">
-        <v>6614615</v>
+        <v>6614631</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1704,7 +1699,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1709,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>22:06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>satt med huvudet upp över ytan.</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -1745,7 +1745,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122357299</v>
+        <v>122356806</v>
       </c>
       <c r="B11" t="n">
         <v>57744</v>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>666863</v>
+        <v>666810</v>
       </c>
       <c r="R11" t="n">
-        <v>6614722</v>
+        <v>6614633</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,10 +1855,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122356806</v>
+        <v>122356817</v>
       </c>
       <c r="B12" t="n">
-        <v>57744</v>
+        <v>57390</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,20 +1867,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>666810</v>
+        <v>666882</v>
       </c>
       <c r="R12" t="n">
-        <v>6614633</v>
+        <v>6614737</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1965,10 +1965,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122357133</v>
+        <v>122357299</v>
       </c>
       <c r="B13" t="n">
-        <v>56826</v>
+        <v>57744</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1981,16 +1981,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102954</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>666888</v>
+        <v>666863</v>
       </c>
       <c r="R13" t="n">
-        <v>6614627</v>
+        <v>6614722</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2043,12 +2043,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2075,10 +2075,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122357198</v>
+        <v>122357133</v>
       </c>
       <c r="B14" t="n">
-        <v>58079</v>
+        <v>56826</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2087,30 +2087,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>666822</v>
+        <v>666888</v>
       </c>
       <c r="R14" t="n">
-        <v>6614911</v>
+        <v>6614627</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2185,10 +2185,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122357200</v>
+        <v>122357198</v>
       </c>
       <c r="B15" t="n">
-        <v>56826</v>
+        <v>58079</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2197,28 +2197,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102954</v>
+        <v>103055</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
@@ -2229,10 +2233,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>666857</v>
+        <v>666822</v>
       </c>
       <c r="R15" t="n">
-        <v>6614899</v>
+        <v>6614911</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2291,10 +2295,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122356817</v>
+        <v>122357200</v>
       </c>
       <c r="B16" t="n">
-        <v>57390</v>
+        <v>56826</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,20 +2307,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>102954</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2324,11 +2328,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>666882</v>
+        <v>666857</v>
       </c>
       <c r="R16" t="n">
-        <v>6614737</v>
+        <v>6614899</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2369,12 +2369,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -1745,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122356806</v>
+        <v>122357200</v>
       </c>
       <c r="B11" t="n">
-        <v>57744</v>
+        <v>56826</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1761,16 +1761,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>102954</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1778,11 +1778,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
@@ -1793,10 +1789,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>666810</v>
+        <v>666857</v>
       </c>
       <c r="R11" t="n">
-        <v>6614633</v>
+        <v>6614899</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1823,12 +1819,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -2295,10 +2291,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122357200</v>
+        <v>122356806</v>
       </c>
       <c r="B16" t="n">
-        <v>56826</v>
+        <v>57744</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2311,16 +2307,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102954</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2328,7 +2324,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>666857</v>
+        <v>666810</v>
       </c>
       <c r="R16" t="n">
-        <v>6614899</v>
+        <v>6614633</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2369,12 +2369,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1745,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122357200</v>
+        <v>122356817</v>
       </c>
       <c r="B11" t="n">
-        <v>56826</v>
+        <v>57390</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,20 +1757,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102954</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1778,7 +1778,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
@@ -1789,10 +1793,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>666857</v>
+        <v>666882</v>
       </c>
       <c r="R11" t="n">
-        <v>6614899</v>
+        <v>6614737</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1819,12 +1823,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,10 +1855,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122356817</v>
+        <v>122357200</v>
       </c>
       <c r="B12" t="n">
-        <v>57390</v>
+        <v>56826</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1863,20 +1867,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>102954</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1884,11 +1888,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>666882</v>
+        <v>666857</v>
       </c>
       <c r="R12" t="n">
-        <v>6614737</v>
+        <v>6614899</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1929,12 +1929,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1961,10 +1961,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122357299</v>
+        <v>122357133</v>
       </c>
       <c r="B13" t="n">
-        <v>57744</v>
+        <v>56826</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1977,16 +1977,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>102954</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>666863</v>
+        <v>666888</v>
       </c>
       <c r="R13" t="n">
-        <v>6614722</v>
+        <v>6614627</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2071,10 +2071,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122357133</v>
+        <v>122357198</v>
       </c>
       <c r="B14" t="n">
-        <v>56826</v>
+        <v>58079</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2083,30 +2083,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102954</v>
+        <v>103055</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>666888</v>
+        <v>666822</v>
       </c>
       <c r="R14" t="n">
-        <v>6614627</v>
+        <v>6614911</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122357198</v>
+        <v>122356806</v>
       </c>
       <c r="B15" t="n">
-        <v>58079</v>
+        <v>57744</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2193,30 +2193,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103055</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -2229,10 +2229,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>666822</v>
+        <v>666810</v>
       </c>
       <c r="R15" t="n">
-        <v>6614911</v>
+        <v>6614633</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2259,12 +2259,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,7 +2291,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122356806</v>
+        <v>122357299</v>
       </c>
       <c r="B16" t="n">
         <v>57744</v>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>666810</v>
+        <v>666863</v>
       </c>
       <c r="R16" t="n">
-        <v>6614633</v>
+        <v>6614722</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2369,12 +2369,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2398,6 +2398,1054 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122440071</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56287</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Arlanda flygplats, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>666884</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6614611</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Torge Gerwin</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jacqueline Nelms, Torge Gerwin, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122440078</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56285</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Arlanda flygplats, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>666884</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6614611</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Torge Gerwin</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jacqueline Nelms, Torge Gerwin, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122440103</v>
+      </c>
+      <c r="B19" t="n">
+        <v>56266</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Arlanda flygplats, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>666884</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6614611</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Torge Gerwin</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jacqueline Nelms, Torge Gerwin, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122440106</v>
+      </c>
+      <c r="B20" t="n">
+        <v>56266</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Arlanda flygplats, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>666883</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6614610</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Torge Gerwin</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jacqueline Nelms, Torge Gerwin, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122440097</v>
+      </c>
+      <c r="B21" t="n">
+        <v>56273</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Arlanda flygplats, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>666884</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6614611</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Torge Gerwin</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jacqueline Nelms, Torge Gerwin, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>122440085</v>
+      </c>
+      <c r="B22" t="n">
+        <v>56280</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Arlanda flygplats, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>666884</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6614611</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Torge Gerwin</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jacqueline Nelms, Torge Gerwin, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>122440088</v>
+      </c>
+      <c r="B23" t="n">
+        <v>56280</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Arlanda flygplats, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>666883</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6614610</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Torge Gerwin</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jacqueline Nelms, Torge Gerwin, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>122440081</v>
+      </c>
+      <c r="B24" t="n">
+        <v>56285</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Arlanda flygplats, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>666883</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6614610</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Torge Gerwin</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jacqueline Nelms, Torge Gerwin, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -1745,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122356817</v>
+        <v>122357133</v>
       </c>
       <c r="B11" t="n">
-        <v>57390</v>
+        <v>56831</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,20 +1757,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>102954</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>666882</v>
+        <v>666888</v>
       </c>
       <c r="R11" t="n">
-        <v>6614737</v>
+        <v>6614627</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,10 +1855,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122357200</v>
+        <v>122356817</v>
       </c>
       <c r="B12" t="n">
-        <v>56826</v>
+        <v>57395</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,20 +1867,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102954</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1888,7 +1888,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
@@ -1899,10 +1903,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>666857</v>
+        <v>666882</v>
       </c>
       <c r="R12" t="n">
-        <v>6614899</v>
+        <v>6614737</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1929,12 +1933,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1961,10 +1965,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122357133</v>
+        <v>122357198</v>
       </c>
       <c r="B13" t="n">
-        <v>56826</v>
+        <v>58084</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1973,30 +1977,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102954</v>
+        <v>103055</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -2009,10 +2013,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>666888</v>
+        <v>666822</v>
       </c>
       <c r="R13" t="n">
-        <v>6614627</v>
+        <v>6614911</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2071,10 +2075,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122357198</v>
+        <v>122357200</v>
       </c>
       <c r="B14" t="n">
-        <v>58079</v>
+        <v>56831</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2083,32 +2087,28 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>666822</v>
+        <v>666857</v>
       </c>
       <c r="R14" t="n">
-        <v>6614911</v>
+        <v>6614899</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122356806</v>
+        <v>122357299</v>
       </c>
       <c r="B15" t="n">
-        <v>57744</v>
+        <v>57749</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -2229,10 +2229,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>666810</v>
+        <v>666863</v>
       </c>
       <c r="R15" t="n">
-        <v>6614633</v>
+        <v>6614722</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2259,12 +2259,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,10 +2291,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122357299</v>
+        <v>122356806</v>
       </c>
       <c r="B16" t="n">
-        <v>57744</v>
+        <v>57749</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2326,7 +2326,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>666863</v>
+        <v>666810</v>
       </c>
       <c r="R16" t="n">
-        <v>6614722</v>
+        <v>6614633</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2369,12 +2369,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2401,10 +2401,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122440071</v>
+        <v>122440103</v>
       </c>
       <c r="B17" t="n">
-        <v>56287</v>
+        <v>56271</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2417,26 +2417,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2532,10 +2532,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122440078</v>
+        <v>122440106</v>
       </c>
       <c r="B18" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2544,30 +2544,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>666884</v>
+        <v>666883</v>
       </c>
       <c r="R18" t="n">
-        <v>6614611</v>
+        <v>6614610</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2621,22 +2621,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2663,10 +2663,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122440103</v>
+        <v>122440081</v>
       </c>
       <c r="B19" t="n">
-        <v>56266</v>
+        <v>56290</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2675,30 +2675,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>666884</v>
+        <v>666883</v>
       </c>
       <c r="R19" t="n">
-        <v>6614611</v>
+        <v>6614610</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2752,22 +2752,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2794,10 +2794,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122440106</v>
+        <v>122440071</v>
       </c>
       <c r="B20" t="n">
-        <v>56266</v>
+        <v>56292</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2810,26 +2810,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>205998</v>
+        <v>206002</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>666883</v>
+        <v>666884</v>
       </c>
       <c r="R20" t="n">
-        <v>6614610</v>
+        <v>6614611</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2883,22 +2883,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2925,10 +2925,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122440097</v>
+        <v>122440085</v>
       </c>
       <c r="B21" t="n">
-        <v>56273</v>
+        <v>56285</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2941,26 +2941,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3056,10 +3056,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122440085</v>
+        <v>122440097</v>
       </c>
       <c r="B22" t="n">
-        <v>56280</v>
+        <v>56278</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3072,26 +3072,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3187,10 +3187,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122440088</v>
+        <v>122440078</v>
       </c>
       <c r="B23" t="n">
-        <v>56280</v>
+        <v>56290</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3203,26 +3203,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>666883</v>
+        <v>666884</v>
       </c>
       <c r="R23" t="n">
-        <v>6614610</v>
+        <v>6614611</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3276,22 +3276,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3318,7 +3318,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122440081</v>
+        <v>122440088</v>
       </c>
       <c r="B24" t="n">
         <v>56285</v>
@@ -3334,26 +3334,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -1745,7 +1745,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122357133</v>
+        <v>122357200</v>
       </c>
       <c r="B11" t="n">
         <v>56831</v>
@@ -1778,11 +1778,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
@@ -1793,10 +1789,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>666888</v>
+        <v>666857</v>
       </c>
       <c r="R11" t="n">
-        <v>6614627</v>
+        <v>6614899</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1855,10 +1851,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122356817</v>
+        <v>122357299</v>
       </c>
       <c r="B12" t="n">
-        <v>57395</v>
+        <v>57749</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,20 +1863,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1903,10 +1899,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>666882</v>
+        <v>666863</v>
       </c>
       <c r="R12" t="n">
-        <v>6614737</v>
+        <v>6614722</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1933,12 +1929,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1965,10 +1961,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122357198</v>
+        <v>122356806</v>
       </c>
       <c r="B13" t="n">
-        <v>58084</v>
+        <v>57749</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1977,30 +1973,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103055</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -2013,10 +2009,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>666822</v>
+        <v>666810</v>
       </c>
       <c r="R13" t="n">
-        <v>6614911</v>
+        <v>6614633</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2043,12 +2039,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2075,10 +2071,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122357200</v>
+        <v>122356817</v>
       </c>
       <c r="B14" t="n">
-        <v>56831</v>
+        <v>57395</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2087,20 +2083,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102954</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2108,7 +2104,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>666857</v>
+        <v>666882</v>
       </c>
       <c r="R14" t="n">
-        <v>6614899</v>
+        <v>6614737</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2149,12 +2149,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2181,10 +2181,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122357299</v>
+        <v>122357198</v>
       </c>
       <c r="B15" t="n">
-        <v>57749</v>
+        <v>58084</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2193,25 +2193,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>103055</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2229,10 +2229,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>666863</v>
+        <v>666822</v>
       </c>
       <c r="R15" t="n">
-        <v>6614722</v>
+        <v>6614911</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2259,12 +2259,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,10 +2291,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122356806</v>
+        <v>122357133</v>
       </c>
       <c r="B16" t="n">
-        <v>57749</v>
+        <v>56831</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2307,16 +2307,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>102954</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>666810</v>
+        <v>666888</v>
       </c>
       <c r="R16" t="n">
-        <v>6614633</v>
+        <v>6614627</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2369,12 +2369,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2401,10 +2401,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122440103</v>
+        <v>122440081</v>
       </c>
       <c r="B17" t="n">
-        <v>56271</v>
+        <v>56290</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2413,30 +2413,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>666884</v>
+        <v>666883</v>
       </c>
       <c r="R17" t="n">
-        <v>6614611</v>
+        <v>6614610</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2490,22 +2490,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2532,10 +2532,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122440106</v>
+        <v>122440088</v>
       </c>
       <c r="B18" t="n">
-        <v>56271</v>
+        <v>56285</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2544,30 +2544,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2663,10 +2663,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122440081</v>
+        <v>122440097</v>
       </c>
       <c r="B19" t="n">
-        <v>56290</v>
+        <v>56278</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2679,26 +2679,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>666883</v>
+        <v>666884</v>
       </c>
       <c r="R19" t="n">
-        <v>6614610</v>
+        <v>6614611</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2752,22 +2752,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2794,10 +2794,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122440071</v>
+        <v>122440078</v>
       </c>
       <c r="B20" t="n">
-        <v>56292</v>
+        <v>56290</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2806,25 +2806,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2925,10 +2925,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122440085</v>
+        <v>122440071</v>
       </c>
       <c r="B21" t="n">
-        <v>56285</v>
+        <v>56292</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2937,30 +2937,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100092</v>
+        <v>206002</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3056,10 +3056,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122440097</v>
+        <v>122440085</v>
       </c>
       <c r="B22" t="n">
-        <v>56278</v>
+        <v>56285</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3072,26 +3072,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3187,10 +3187,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122440078</v>
+        <v>122440106</v>
       </c>
       <c r="B23" t="n">
-        <v>56290</v>
+        <v>56271</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3199,30 +3199,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>666884</v>
+        <v>666883</v>
       </c>
       <c r="R23" t="n">
-        <v>6614611</v>
+        <v>6614610</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3276,22 +3276,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3318,10 +3318,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122440088</v>
+        <v>122440103</v>
       </c>
       <c r="B24" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3330,30 +3330,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>666883</v>
+        <v>666884</v>
       </c>
       <c r="R24" t="n">
-        <v>6614610</v>
+        <v>6614611</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3407,22 +3407,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -1745,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122357200</v>
+        <v>122356817</v>
       </c>
       <c r="B11" t="n">
-        <v>56831</v>
+        <v>57395</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,20 +1757,15 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102954</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Enkelbeckasin</t>
-        </is>
+        <v>100049</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1778,7 +1773,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
@@ -1789,10 +1788,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>666857</v>
+        <v>666882</v>
       </c>
       <c r="R11" t="n">
-        <v>6614899</v>
+        <v>6614737</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1819,12 +1818,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,10 +1850,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122357299</v>
+        <v>122357133</v>
       </c>
       <c r="B12" t="n">
-        <v>57749</v>
+        <v>56831</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,16 +1866,11 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
+        <v>102954</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1886,7 +1880,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1899,10 +1893,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>666863</v>
+        <v>666888</v>
       </c>
       <c r="R12" t="n">
-        <v>6614722</v>
+        <v>6614627</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1929,12 +1923,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1961,10 +1955,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122356806</v>
+        <v>122357198</v>
       </c>
       <c r="B13" t="n">
-        <v>57749</v>
+        <v>58084</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1973,30 +1967,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Kungsfågel</t>
-        </is>
+        <v>103055</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -2009,10 +1998,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>666810</v>
+        <v>666822</v>
       </c>
       <c r="R13" t="n">
-        <v>6614633</v>
+        <v>6614911</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2039,12 +2028,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2071,10 +2060,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122356817</v>
+        <v>122357200</v>
       </c>
       <c r="B14" t="n">
-        <v>57395</v>
+        <v>56831</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2083,20 +2072,15 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>102954</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2104,11 +2088,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
@@ -2119,10 +2099,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>666882</v>
+        <v>666857</v>
       </c>
       <c r="R14" t="n">
-        <v>6614737</v>
+        <v>6614899</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2149,12 +2129,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2181,10 +2161,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122357198</v>
+        <v>122357299</v>
       </c>
       <c r="B15" t="n">
-        <v>58084</v>
+        <v>57749</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2193,25 +2173,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103055</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Gulsparv</t>
-        </is>
+        <v>103015</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2229,10 +2204,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>666822</v>
+        <v>666863</v>
       </c>
       <c r="R15" t="n">
-        <v>6614911</v>
+        <v>6614722</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2259,12 +2234,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,10 +2266,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122357133</v>
+        <v>122356806</v>
       </c>
       <c r="B16" t="n">
-        <v>56831</v>
+        <v>57749</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2307,16 +2282,11 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102954</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Enkelbeckasin</t>
-        </is>
+        <v>103015</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2339,10 +2309,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>666888</v>
+        <v>666810</v>
       </c>
       <c r="R16" t="n">
-        <v>6614627</v>
+        <v>6614633</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2369,12 +2339,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2401,10 +2371,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122440081</v>
+        <v>122440097</v>
       </c>
       <c r="B17" t="n">
-        <v>56290</v>
+        <v>56278</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2417,26 +2387,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>205992</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2460,10 +2425,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>666883</v>
+        <v>666884</v>
       </c>
       <c r="R17" t="n">
-        <v>6614610</v>
+        <v>6614611</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2490,22 +2455,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2532,10 +2497,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122440088</v>
+        <v>122440103</v>
       </c>
       <c r="B18" t="n">
-        <v>56285</v>
+        <v>56271</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2544,30 +2509,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>205998</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2591,10 +2551,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>666883</v>
+        <v>666884</v>
       </c>
       <c r="R18" t="n">
-        <v>6614610</v>
+        <v>6614611</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2621,22 +2581,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2663,10 +2623,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122440097</v>
+        <v>122440085</v>
       </c>
       <c r="B19" t="n">
-        <v>56278</v>
+        <v>56285</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2679,26 +2639,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205992</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Vattenfladdermus</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2794,10 +2749,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122440078</v>
+        <v>122440088</v>
       </c>
       <c r="B20" t="n">
-        <v>56290</v>
+        <v>56285</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2810,26 +2765,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>205995</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Dvärgpipistrell</t>
-        </is>
+        <v>100092</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2853,10 +2803,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>666884</v>
+        <v>666883</v>
       </c>
       <c r="R20" t="n">
-        <v>6614611</v>
+        <v>6614610</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2883,22 +2833,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2925,10 +2875,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122440071</v>
+        <v>122440078</v>
       </c>
       <c r="B21" t="n">
-        <v>56292</v>
+        <v>56290</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2937,25 +2887,20 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>206002</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Brunlångöra</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3056,10 +3001,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122440085</v>
+        <v>122440081</v>
       </c>
       <c r="B22" t="n">
-        <v>56285</v>
+        <v>56290</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3072,26 +3017,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100092</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Större brunfladdermus</t>
-        </is>
+        <v>205995</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3115,10 +3055,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>666884</v>
+        <v>666883</v>
       </c>
       <c r="R22" t="n">
-        <v>6614611</v>
+        <v>6614610</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3145,22 +3085,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3187,10 +3127,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122440106</v>
+        <v>122440071</v>
       </c>
       <c r="B23" t="n">
-        <v>56271</v>
+        <v>56292</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3203,26 +3143,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>205998</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
+        <v>206002</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3246,10 +3181,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>666883</v>
+        <v>666884</v>
       </c>
       <c r="R23" t="n">
-        <v>6614610</v>
+        <v>6614611</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3276,22 +3211,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3318,7 +3253,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122440103</v>
+        <v>122440106</v>
       </c>
       <c r="B24" t="n">
         <v>56271</v>
@@ -3336,11 +3271,6 @@
       <c r="E24" t="n">
         <v>205998</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Nordfladdermus</t>
-        </is>
-      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>Eptesicus nilssonii</t>
@@ -3353,7 +3283,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3377,10 +3307,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>666884</v>
+        <v>666883</v>
       </c>
       <c r="R24" t="n">
-        <v>6614611</v>
+        <v>6614610</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3407,22 +3337,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -1745,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122356817</v>
+        <v>122357299</v>
       </c>
       <c r="B11" t="n">
-        <v>57395</v>
+        <v>57753</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,15 +1757,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103015</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1788,10 +1793,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>666882</v>
+        <v>666863</v>
       </c>
       <c r="R11" t="n">
-        <v>6614737</v>
+        <v>6614722</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1818,12 +1823,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1850,10 +1855,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122357133</v>
+        <v>122356806</v>
       </c>
       <c r="B12" t="n">
-        <v>56831</v>
+        <v>57753</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1866,11 +1871,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102954</v>
+        <v>103015</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1893,10 +1903,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>666888</v>
+        <v>666810</v>
       </c>
       <c r="R12" t="n">
-        <v>6614627</v>
+        <v>6614633</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1923,12 +1933,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,7 +1968,7 @@
         <v>122357198</v>
       </c>
       <c r="B13" t="n">
-        <v>58084</v>
+        <v>58088</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1972,6 +1982,11 @@
       </c>
       <c r="E13" t="n">
         <v>103055</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2060,10 +2075,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122357200</v>
+        <v>122357133</v>
       </c>
       <c r="B14" t="n">
-        <v>56831</v>
+        <v>56835</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2078,6 +2093,11 @@
       <c r="E14" t="n">
         <v>102954</v>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Gallinago gallinago</t>
@@ -2088,7 +2108,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
@@ -2099,10 +2123,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>666857</v>
+        <v>666888</v>
       </c>
       <c r="R14" t="n">
-        <v>6614899</v>
+        <v>6614627</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2161,10 +2185,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122357299</v>
+        <v>122356817</v>
       </c>
       <c r="B15" t="n">
-        <v>57749</v>
+        <v>57399</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2173,15 +2197,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>100049</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2204,10 +2233,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>666863</v>
+        <v>666882</v>
       </c>
       <c r="R15" t="n">
-        <v>6614722</v>
+        <v>6614737</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2234,12 +2263,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2266,10 +2295,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122356806</v>
+        <v>122357200</v>
       </c>
       <c r="B16" t="n">
-        <v>57749</v>
+        <v>56835</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2282,11 +2311,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>102954</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Enkelbeckasin</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2294,11 +2328,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
@@ -2309,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>666810</v>
+        <v>666857</v>
       </c>
       <c r="R16" t="n">
-        <v>6614633</v>
+        <v>6614899</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2339,12 +2369,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2371,10 +2401,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122440097</v>
+        <v>122440088</v>
       </c>
       <c r="B17" t="n">
-        <v>56278</v>
+        <v>56289</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2387,21 +2417,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205992</v>
+        <v>100092</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2425,10 +2460,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>666884</v>
+        <v>666883</v>
       </c>
       <c r="R17" t="n">
-        <v>6614611</v>
+        <v>6614610</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2455,22 +2490,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2497,10 +2532,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122440103</v>
+        <v>122440078</v>
       </c>
       <c r="B18" t="n">
-        <v>56271</v>
+        <v>56294</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2509,25 +2544,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205998</v>
+        <v>205995</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2623,10 +2663,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122440085</v>
+        <v>122440081</v>
       </c>
       <c r="B19" t="n">
-        <v>56285</v>
+        <v>56294</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2639,21 +2679,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100092</v>
+        <v>205995</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2677,10 +2722,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>666884</v>
+        <v>666883</v>
       </c>
       <c r="R19" t="n">
-        <v>6614611</v>
+        <v>6614610</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2707,22 +2752,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2749,10 +2794,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122440088</v>
+        <v>122440106</v>
       </c>
       <c r="B20" t="n">
-        <v>56285</v>
+        <v>56275</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2761,25 +2806,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100092</v>
+        <v>205998</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2875,10 +2925,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122440078</v>
+        <v>122440103</v>
       </c>
       <c r="B21" t="n">
-        <v>56290</v>
+        <v>56275</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2887,25 +2937,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>205995</v>
+        <v>205998</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3001,10 +3056,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122440081</v>
+        <v>122440085</v>
       </c>
       <c r="B22" t="n">
-        <v>56290</v>
+        <v>56289</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3017,21 +3072,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>205995</v>
+        <v>100092</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3055,10 +3115,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>666883</v>
+        <v>666884</v>
       </c>
       <c r="R22" t="n">
-        <v>6614610</v>
+        <v>6614611</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3085,22 +3145,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3130,7 +3190,7 @@
         <v>122440071</v>
       </c>
       <c r="B23" t="n">
-        <v>56292</v>
+        <v>56296</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3144,6 +3204,11 @@
       </c>
       <c r="E23" t="n">
         <v>206002</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -3253,10 +3318,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122440106</v>
+        <v>122440097</v>
       </c>
       <c r="B24" t="n">
-        <v>56271</v>
+        <v>56282</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3265,25 +3330,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>205998</v>
+        <v>205992</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3307,10 +3377,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>666883</v>
+        <v>666884</v>
       </c>
       <c r="R24" t="n">
-        <v>6614610</v>
+        <v>6614611</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3337,22 +3407,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -1745,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122357299</v>
+        <v>122357133</v>
       </c>
       <c r="B11" t="n">
-        <v>57753</v>
+        <v>56835</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1761,16 +1761,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>102954</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>666863</v>
+        <v>666888</v>
       </c>
       <c r="R11" t="n">
-        <v>6614722</v>
+        <v>6614627</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,7 +1855,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122356806</v>
+        <v>122357299</v>
       </c>
       <c r="B12" t="n">
         <v>57753</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>666810</v>
+        <v>666863</v>
       </c>
       <c r="R12" t="n">
-        <v>6614633</v>
+        <v>6614722</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1965,10 +1965,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122357198</v>
+        <v>122356817</v>
       </c>
       <c r="B13" t="n">
-        <v>58088</v>
+        <v>57399</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1981,21 +1981,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103055</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>666822</v>
+        <v>666882</v>
       </c>
       <c r="R13" t="n">
-        <v>6614911</v>
+        <v>6614737</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2043,12 +2043,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2075,10 +2075,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122357133</v>
+        <v>122357198</v>
       </c>
       <c r="B14" t="n">
-        <v>56835</v>
+        <v>58088</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2087,30 +2087,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102954</v>
+        <v>103055</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>666888</v>
+        <v>666822</v>
       </c>
       <c r="R14" t="n">
-        <v>6614627</v>
+        <v>6614911</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2185,10 +2185,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122356817</v>
+        <v>122357200</v>
       </c>
       <c r="B15" t="n">
-        <v>57399</v>
+        <v>56835</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2197,20 +2197,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>102954</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2218,11 +2218,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
@@ -2233,10 +2229,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>666882</v>
+        <v>666857</v>
       </c>
       <c r="R15" t="n">
-        <v>6614737</v>
+        <v>6614899</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2263,12 +2259,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2295,10 +2291,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122357200</v>
+        <v>122356806</v>
       </c>
       <c r="B16" t="n">
-        <v>56835</v>
+        <v>57753</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2311,16 +2307,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102954</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2328,7 +2324,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>666857</v>
+        <v>666810</v>
       </c>
       <c r="R16" t="n">
-        <v>6614899</v>
+        <v>6614633</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2369,12 +2369,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2532,7 +2532,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122440078</v>
+        <v>122440081</v>
       </c>
       <c r="B18" t="n">
         <v>56294</v>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>666884</v>
+        <v>666883</v>
       </c>
       <c r="R18" t="n">
-        <v>6614611</v>
+        <v>6614610</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2621,22 +2621,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2663,10 +2663,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122440081</v>
+        <v>122440103</v>
       </c>
       <c r="B19" t="n">
-        <v>56294</v>
+        <v>56275</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2675,30 +2675,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>666883</v>
+        <v>666884</v>
       </c>
       <c r="R19" t="n">
-        <v>6614610</v>
+        <v>6614611</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2752,22 +2752,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2794,10 +2794,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122440106</v>
+        <v>122440071</v>
       </c>
       <c r="B20" t="n">
-        <v>56275</v>
+        <v>56296</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2810,26 +2810,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>205998</v>
+        <v>206002</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>666883</v>
+        <v>666884</v>
       </c>
       <c r="R20" t="n">
-        <v>6614610</v>
+        <v>6614611</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2883,22 +2883,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2925,10 +2925,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122440103</v>
+        <v>122440078</v>
       </c>
       <c r="B21" t="n">
-        <v>56275</v>
+        <v>56294</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2937,30 +2937,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3056,10 +3056,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122440085</v>
+        <v>122440097</v>
       </c>
       <c r="B22" t="n">
-        <v>56289</v>
+        <v>56282</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3072,26 +3072,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3187,10 +3187,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122440071</v>
+        <v>122440106</v>
       </c>
       <c r="B23" t="n">
-        <v>56296</v>
+        <v>56275</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3203,26 +3203,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>666884</v>
+        <v>666883</v>
       </c>
       <c r="R23" t="n">
-        <v>6614611</v>
+        <v>6614610</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3276,22 +3276,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3318,10 +3318,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122440097</v>
+        <v>122440085</v>
       </c>
       <c r="B24" t="n">
-        <v>56282</v>
+        <v>56289</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3334,26 +3334,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -1745,7 +1745,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122357133</v>
+        <v>122357200</v>
       </c>
       <c r="B11" t="n">
         <v>56835</v>
@@ -1778,11 +1778,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
@@ -1793,10 +1789,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>666888</v>
+        <v>666857</v>
       </c>
       <c r="R11" t="n">
-        <v>6614627</v>
+        <v>6614899</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1855,7 +1851,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122357299</v>
+        <v>122356806</v>
       </c>
       <c r="B12" t="n">
         <v>57753</v>
@@ -1890,7 +1886,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1903,10 +1899,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>666863</v>
+        <v>666810</v>
       </c>
       <c r="R12" t="n">
-        <v>6614722</v>
+        <v>6614633</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1933,12 +1929,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1965,10 +1961,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122356817</v>
+        <v>122357198</v>
       </c>
       <c r="B13" t="n">
-        <v>57399</v>
+        <v>58088</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1981,21 +1977,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>103055</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2013,10 +2009,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>666882</v>
+        <v>666822</v>
       </c>
       <c r="R13" t="n">
-        <v>6614737</v>
+        <v>6614911</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2043,12 +2039,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2075,10 +2071,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122357198</v>
+        <v>122357133</v>
       </c>
       <c r="B14" t="n">
-        <v>58088</v>
+        <v>56835</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2087,30 +2083,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2123,10 +2119,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>666822</v>
+        <v>666888</v>
       </c>
       <c r="R14" t="n">
-        <v>6614911</v>
+        <v>6614627</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2185,10 +2181,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122357200</v>
+        <v>122357299</v>
       </c>
       <c r="B15" t="n">
-        <v>56835</v>
+        <v>57753</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2201,16 +2197,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102954</v>
+        <v>103015</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2218,7 +2214,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
@@ -2229,10 +2229,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>666857</v>
+        <v>666863</v>
       </c>
       <c r="R15" t="n">
-        <v>6614899</v>
+        <v>6614722</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2259,12 +2259,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,10 +2291,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122356806</v>
+        <v>122356817</v>
       </c>
       <c r="B16" t="n">
-        <v>57753</v>
+        <v>57399</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,20 +2303,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>666810</v>
+        <v>666882</v>
       </c>
       <c r="R16" t="n">
-        <v>6614633</v>
+        <v>6614737</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122440088</v>
+        <v>122440071</v>
       </c>
       <c r="B17" t="n">
-        <v>56289</v>
+        <v>56296</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2413,30 +2413,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100092</v>
+        <v>206002</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>666883</v>
+        <v>666884</v>
       </c>
       <c r="R17" t="n">
-        <v>6614610</v>
+        <v>6614611</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2490,22 +2490,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2532,7 +2532,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122440081</v>
+        <v>122440078</v>
       </c>
       <c r="B18" t="n">
         <v>56294</v>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>666883</v>
+        <v>666884</v>
       </c>
       <c r="R18" t="n">
-        <v>6614610</v>
+        <v>6614611</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2621,22 +2621,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2663,10 +2663,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122440103</v>
+        <v>122440097</v>
       </c>
       <c r="B19" t="n">
-        <v>56275</v>
+        <v>56282</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2675,30 +2675,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2794,10 +2794,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122440071</v>
+        <v>122440103</v>
       </c>
       <c r="B20" t="n">
-        <v>56296</v>
+        <v>56275</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2810,26 +2810,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2925,7 +2925,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122440078</v>
+        <v>122440081</v>
       </c>
       <c r="B21" t="n">
         <v>56294</v>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>666884</v>
+        <v>666883</v>
       </c>
       <c r="R21" t="n">
-        <v>6614611</v>
+        <v>6614610</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3056,10 +3056,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122440097</v>
+        <v>122440085</v>
       </c>
       <c r="B22" t="n">
-        <v>56282</v>
+        <v>56289</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3072,26 +3072,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3187,10 +3187,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122440106</v>
+        <v>122440088</v>
       </c>
       <c r="B23" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3199,30 +3199,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3318,10 +3318,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122440085</v>
+        <v>122440106</v>
       </c>
       <c r="B24" t="n">
-        <v>56289</v>
+        <v>56275</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3330,30 +3330,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>666884</v>
+        <v>666883</v>
       </c>
       <c r="R24" t="n">
-        <v>6614611</v>
+        <v>6614610</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3407,22 +3407,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -1745,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122357200</v>
+        <v>122357299</v>
       </c>
       <c r="B11" t="n">
-        <v>56835</v>
+        <v>57753</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1761,16 +1761,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102954</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1778,7 +1778,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
@@ -1789,10 +1793,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>666857</v>
+        <v>666863</v>
       </c>
       <c r="R11" t="n">
-        <v>6614899</v>
+        <v>6614722</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1819,12 +1823,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,10 +1855,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122356806</v>
+        <v>122357198</v>
       </c>
       <c r="B12" t="n">
-        <v>57753</v>
+        <v>58088</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1863,30 +1867,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>103055</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1899,10 +1903,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>666810</v>
+        <v>666822</v>
       </c>
       <c r="R12" t="n">
-        <v>6614633</v>
+        <v>6614911</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1929,12 +1933,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1961,10 +1965,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122357198</v>
+        <v>122357133</v>
       </c>
       <c r="B13" t="n">
-        <v>58088</v>
+        <v>56835</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1973,30 +1977,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -2009,10 +2013,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>666822</v>
+        <v>666888</v>
       </c>
       <c r="R13" t="n">
-        <v>6614911</v>
+        <v>6614627</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2071,10 +2075,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122357133</v>
+        <v>122356817</v>
       </c>
       <c r="B14" t="n">
-        <v>56835</v>
+        <v>57399</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2083,20 +2087,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102954</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2106,7 +2110,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2119,10 +2123,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>666888</v>
+        <v>666882</v>
       </c>
       <c r="R14" t="n">
-        <v>6614627</v>
+        <v>6614737</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2149,12 +2153,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2181,10 +2185,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122357299</v>
+        <v>122357200</v>
       </c>
       <c r="B15" t="n">
-        <v>57753</v>
+        <v>56835</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2197,16 +2201,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103015</v>
+        <v>102954</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2214,11 +2218,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
@@ -2229,10 +2229,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>666863</v>
+        <v>666857</v>
       </c>
       <c r="R15" t="n">
-        <v>6614722</v>
+        <v>6614899</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2259,12 +2259,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,10 +2291,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122356817</v>
+        <v>122356806</v>
       </c>
       <c r="B16" t="n">
-        <v>57399</v>
+        <v>57753</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,20 +2303,20 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>666882</v>
+        <v>666810</v>
       </c>
       <c r="R16" t="n">
-        <v>6614737</v>
+        <v>6614633</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122440071</v>
+        <v>122440085</v>
       </c>
       <c r="B17" t="n">
-        <v>56296</v>
+        <v>56289</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2413,30 +2413,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>206002</v>
+        <v>100092</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2532,7 +2532,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122440078</v>
+        <v>122440081</v>
       </c>
       <c r="B18" t="n">
         <v>56294</v>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>666884</v>
+        <v>666883</v>
       </c>
       <c r="R18" t="n">
-        <v>6614611</v>
+        <v>6614610</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2621,22 +2621,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2663,10 +2663,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122440097</v>
+        <v>122440106</v>
       </c>
       <c r="B19" t="n">
-        <v>56282</v>
+        <v>56275</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2675,30 +2675,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205992</v>
+        <v>205998</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>666884</v>
+        <v>666883</v>
       </c>
       <c r="R19" t="n">
-        <v>6614611</v>
+        <v>6614610</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2752,22 +2752,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2794,10 +2794,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122440103</v>
+        <v>122440078</v>
       </c>
       <c r="B20" t="n">
-        <v>56275</v>
+        <v>56294</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2806,30 +2806,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2925,10 +2925,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122440081</v>
+        <v>122440103</v>
       </c>
       <c r="B21" t="n">
-        <v>56294</v>
+        <v>56275</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2937,30 +2937,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>666883</v>
+        <v>666884</v>
       </c>
       <c r="R21" t="n">
-        <v>6614610</v>
+        <v>6614611</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3056,10 +3056,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122440085</v>
+        <v>122440071</v>
       </c>
       <c r="B22" t="n">
-        <v>56289</v>
+        <v>56296</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3068,30 +3068,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100092</v>
+        <v>206002</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3318,10 +3318,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122440106</v>
+        <v>122440097</v>
       </c>
       <c r="B24" t="n">
-        <v>56275</v>
+        <v>56282</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3330,30 +3330,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>666883</v>
+        <v>666884</v>
       </c>
       <c r="R24" t="n">
-        <v>6614610</v>
+        <v>6614611</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3407,22 +3407,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -1855,10 +1855,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122357198</v>
+        <v>122356817</v>
       </c>
       <c r="B12" t="n">
-        <v>58088</v>
+        <v>57399</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1871,21 +1871,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103055</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>666822</v>
+        <v>666882</v>
       </c>
       <c r="R12" t="n">
-        <v>6614911</v>
+        <v>6614737</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1965,10 +1965,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122357133</v>
+        <v>122357198</v>
       </c>
       <c r="B13" t="n">
-        <v>56835</v>
+        <v>58088</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1977,30 +1977,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102954</v>
+        <v>103055</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>666888</v>
+        <v>666822</v>
       </c>
       <c r="R13" t="n">
-        <v>6614627</v>
+        <v>6614911</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122356817</v>
+        <v>122356806</v>
       </c>
       <c r="B14" t="n">
-        <v>57399</v>
+        <v>57753</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2087,20 +2087,20 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>666882</v>
+        <v>666810</v>
       </c>
       <c r="R14" t="n">
-        <v>6614737</v>
+        <v>6614633</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2185,7 +2185,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122357200</v>
+        <v>122357133</v>
       </c>
       <c r="B15" t="n">
         <v>56835</v>
@@ -2218,7 +2218,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
@@ -2229,10 +2233,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>666857</v>
+        <v>666888</v>
       </c>
       <c r="R15" t="n">
-        <v>6614899</v>
+        <v>6614627</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2291,10 +2295,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122356806</v>
+        <v>122357200</v>
       </c>
       <c r="B16" t="n">
-        <v>57753</v>
+        <v>56835</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2307,16 +2311,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103015</v>
+        <v>102954</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2324,11 +2328,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>666810</v>
+        <v>666857</v>
       </c>
       <c r="R16" t="n">
-        <v>6614633</v>
+        <v>6614899</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2369,12 +2369,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2401,10 +2401,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122440085</v>
+        <v>122440078</v>
       </c>
       <c r="B17" t="n">
-        <v>56289</v>
+        <v>56294</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2417,26 +2417,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2532,10 +2532,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122440081</v>
+        <v>122440103</v>
       </c>
       <c r="B18" t="n">
-        <v>56294</v>
+        <v>56275</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2544,30 +2544,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>666883</v>
+        <v>666884</v>
       </c>
       <c r="R18" t="n">
-        <v>6614610</v>
+        <v>6614611</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2621,22 +2621,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2663,10 +2663,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122440106</v>
+        <v>122440088</v>
       </c>
       <c r="B19" t="n">
-        <v>56275</v>
+        <v>56289</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2675,30 +2675,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2794,10 +2794,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122440078</v>
+        <v>122440085</v>
       </c>
       <c r="B20" t="n">
-        <v>56294</v>
+        <v>56289</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2810,26 +2810,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2925,10 +2925,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122440103</v>
+        <v>122440097</v>
       </c>
       <c r="B21" t="n">
-        <v>56275</v>
+        <v>56282</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2937,30 +2937,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3056,10 +3056,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122440071</v>
+        <v>122440081</v>
       </c>
       <c r="B22" t="n">
-        <v>56296</v>
+        <v>56294</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3068,30 +3068,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>206002</v>
+        <v>205995</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>666884</v>
+        <v>666883</v>
       </c>
       <c r="R22" t="n">
-        <v>6614611</v>
+        <v>6614610</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3145,22 +3145,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3187,10 +3187,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122440088</v>
+        <v>122440106</v>
       </c>
       <c r="B23" t="n">
-        <v>56289</v>
+        <v>56275</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3199,30 +3199,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3318,10 +3318,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122440097</v>
+        <v>122440071</v>
       </c>
       <c r="B24" t="n">
-        <v>56282</v>
+        <v>56296</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3330,25 +3330,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>205992</v>
+        <v>206002</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -1745,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122357299</v>
+        <v>122356806</v>
       </c>
       <c r="B11" t="n">
-        <v>57753</v>
+        <v>57754</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>666863</v>
+        <v>666810</v>
       </c>
       <c r="R11" t="n">
-        <v>6614722</v>
+        <v>6614633</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,10 +1855,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122356817</v>
+        <v>122357198</v>
       </c>
       <c r="B12" t="n">
-        <v>57399</v>
+        <v>58089</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1871,21 +1871,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>103055</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>666882</v>
+        <v>666822</v>
       </c>
       <c r="R12" t="n">
-        <v>6614737</v>
+        <v>6614911</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1965,10 +1965,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122357198</v>
+        <v>122357133</v>
       </c>
       <c r="B13" t="n">
-        <v>58088</v>
+        <v>56836</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1977,30 +1977,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -2013,10 +2013,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>666822</v>
+        <v>666888</v>
       </c>
       <c r="R13" t="n">
-        <v>6614911</v>
+        <v>6614627</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2075,10 +2075,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122356806</v>
+        <v>122357299</v>
       </c>
       <c r="B14" t="n">
-        <v>57753</v>
+        <v>57754</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2123,10 +2123,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>666810</v>
+        <v>666863</v>
       </c>
       <c r="R14" t="n">
-        <v>6614633</v>
+        <v>6614722</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2153,12 +2153,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2185,10 +2185,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122357133</v>
+        <v>122356817</v>
       </c>
       <c r="B15" t="n">
-        <v>56835</v>
+        <v>57400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2197,20 +2197,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102954</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -2233,10 +2233,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>666888</v>
+        <v>666882</v>
       </c>
       <c r="R15" t="n">
-        <v>6614627</v>
+        <v>6614737</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2263,12 +2263,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2298,7 +2298,7 @@
         <v>122357200</v>
       </c>
       <c r="B16" t="n">
-        <v>56835</v>
+        <v>56836</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122440078</v>
+        <v>122440106</v>
       </c>
       <c r="B17" t="n">
-        <v>56294</v>
+        <v>56276</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2413,30 +2413,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>666884</v>
+        <v>666883</v>
       </c>
       <c r="R17" t="n">
-        <v>6614611</v>
+        <v>6614610</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2490,22 +2490,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2532,10 +2532,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122440103</v>
+        <v>122440081</v>
       </c>
       <c r="B18" t="n">
-        <v>56275</v>
+        <v>56295</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2544,30 +2544,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>666884</v>
+        <v>666883</v>
       </c>
       <c r="R18" t="n">
-        <v>6614611</v>
+        <v>6614610</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2621,22 +2621,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2663,10 +2663,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122440088</v>
+        <v>122440103</v>
       </c>
       <c r="B19" t="n">
-        <v>56289</v>
+        <v>56276</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2675,30 +2675,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2722,10 +2722,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>666883</v>
+        <v>666884</v>
       </c>
       <c r="R19" t="n">
-        <v>6614610</v>
+        <v>6614611</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2752,22 +2752,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2794,10 +2794,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122440085</v>
+        <v>122440078</v>
       </c>
       <c r="B20" t="n">
-        <v>56289</v>
+        <v>56295</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2810,26 +2810,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2925,10 +2925,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122440097</v>
+        <v>122440085</v>
       </c>
       <c r="B21" t="n">
-        <v>56282</v>
+        <v>56290</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2941,26 +2941,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3056,10 +3056,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122440081</v>
+        <v>122440071</v>
       </c>
       <c r="B22" t="n">
-        <v>56294</v>
+        <v>56297</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3068,30 +3068,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>205995</v>
+        <v>206002</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>666883</v>
+        <v>666884</v>
       </c>
       <c r="R22" t="n">
-        <v>6614610</v>
+        <v>6614611</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3145,22 +3145,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3187,10 +3187,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122440106</v>
+        <v>122440097</v>
       </c>
       <c r="B23" t="n">
-        <v>56275</v>
+        <v>56283</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3199,30 +3199,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>666883</v>
+        <v>666884</v>
       </c>
       <c r="R23" t="n">
-        <v>6614610</v>
+        <v>6614611</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3276,22 +3276,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3318,10 +3318,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122440071</v>
+        <v>122440088</v>
       </c>
       <c r="B24" t="n">
-        <v>56296</v>
+        <v>56290</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3330,30 +3330,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>206002</v>
+        <v>100092</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3377,10 +3377,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>666884</v>
+        <v>666883</v>
       </c>
       <c r="R24" t="n">
-        <v>6614611</v>
+        <v>6614610</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3407,22 +3407,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -1745,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122356806</v>
+        <v>122356817</v>
       </c>
       <c r="B11" t="n">
-        <v>57754</v>
+        <v>57400</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,20 +1757,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>666810</v>
+        <v>666882</v>
       </c>
       <c r="R11" t="n">
-        <v>6614633</v>
+        <v>6614737</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1855,10 +1855,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122357198</v>
+        <v>122356806</v>
       </c>
       <c r="B12" t="n">
-        <v>58089</v>
+        <v>57754</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,30 +1867,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103055</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1903,10 +1903,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>666822</v>
+        <v>666810</v>
       </c>
       <c r="R12" t="n">
-        <v>6614911</v>
+        <v>6614633</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1933,12 +1933,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1965,7 +1965,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122357133</v>
+        <v>122357200</v>
       </c>
       <c r="B13" t="n">
         <v>56836</v>
@@ -1998,11 +1998,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
@@ -2013,10 +2009,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>666888</v>
+        <v>666857</v>
       </c>
       <c r="R13" t="n">
-        <v>6614627</v>
+        <v>6614899</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2185,10 +2181,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122356817</v>
+        <v>122357133</v>
       </c>
       <c r="B15" t="n">
-        <v>57400</v>
+        <v>56836</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2197,20 +2193,20 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>102954</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2220,7 +2216,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -2233,10 +2229,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>666882</v>
+        <v>666888</v>
       </c>
       <c r="R15" t="n">
-        <v>6614737</v>
+        <v>6614627</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2263,12 +2259,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2295,10 +2291,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122357200</v>
+        <v>122357198</v>
       </c>
       <c r="B16" t="n">
-        <v>56836</v>
+        <v>58089</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2307,28 +2303,32 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102954</v>
+        <v>103055</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>666857</v>
+        <v>666822</v>
       </c>
       <c r="R16" t="n">
-        <v>6614899</v>
+        <v>6614911</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2401,10 +2401,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122440106</v>
+        <v>122440085</v>
       </c>
       <c r="B17" t="n">
-        <v>56276</v>
+        <v>56290</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2413,30 +2413,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>205998</v>
+        <v>100092</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>666883</v>
+        <v>666884</v>
       </c>
       <c r="R17" t="n">
-        <v>6614610</v>
+        <v>6614611</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2490,22 +2490,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2663,10 +2663,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122440103</v>
+        <v>122440071</v>
       </c>
       <c r="B19" t="n">
-        <v>56276</v>
+        <v>56297</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2679,26 +2679,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205998</v>
+        <v>206002</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2794,10 +2794,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122440078</v>
+        <v>122440103</v>
       </c>
       <c r="B20" t="n">
-        <v>56295</v>
+        <v>56276</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2806,30 +2806,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2925,10 +2925,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122440085</v>
+        <v>122440097</v>
       </c>
       <c r="B21" t="n">
-        <v>56290</v>
+        <v>56283</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2941,26 +2941,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3056,10 +3056,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122440071</v>
+        <v>122440106</v>
       </c>
       <c r="B22" t="n">
-        <v>56297</v>
+        <v>56276</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3072,26 +3072,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>666884</v>
+        <v>666883</v>
       </c>
       <c r="R22" t="n">
-        <v>6614611</v>
+        <v>6614610</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3145,22 +3145,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3187,10 +3187,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122440097</v>
+        <v>122440078</v>
       </c>
       <c r="B23" t="n">
-        <v>56283</v>
+        <v>56295</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3203,21 +3203,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>205992</v>
+        <v>205995</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -1745,10 +1745,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122356817</v>
+        <v>122357299</v>
       </c>
       <c r="B11" t="n">
-        <v>57400</v>
+        <v>57754</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1757,20 +1757,20 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>666882</v>
+        <v>666863</v>
       </c>
       <c r="R11" t="n">
-        <v>6614737</v>
+        <v>6614722</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,10 +1855,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122356806</v>
+        <v>122357200</v>
       </c>
       <c r="B12" t="n">
-        <v>57754</v>
+        <v>56836</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1871,16 +1871,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>102954</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1888,11 +1888,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
@@ -1903,10 +1899,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>666810</v>
+        <v>666857</v>
       </c>
       <c r="R12" t="n">
-        <v>6614633</v>
+        <v>6614899</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1933,12 +1929,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1965,10 +1961,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122357200</v>
+        <v>122356806</v>
       </c>
       <c r="B13" t="n">
-        <v>56836</v>
+        <v>57754</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1981,16 +1977,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102954</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1998,7 +1994,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
@@ -2009,10 +2009,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>666857</v>
+        <v>666810</v>
       </c>
       <c r="R13" t="n">
-        <v>6614899</v>
+        <v>6614633</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2039,12 +2039,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2071,10 +2071,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122357299</v>
+        <v>122357198</v>
       </c>
       <c r="B14" t="n">
-        <v>57754</v>
+        <v>58089</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2083,25 +2083,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103015</v>
+        <v>103055</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>666863</v>
+        <v>666822</v>
       </c>
       <c r="R14" t="n">
-        <v>6614722</v>
+        <v>6614911</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2149,12 +2149,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2291,10 +2291,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122357198</v>
+        <v>122356817</v>
       </c>
       <c r="B16" t="n">
-        <v>58089</v>
+        <v>57400</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2307,21 +2307,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103055</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2339,10 +2339,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>666822</v>
+        <v>666882</v>
       </c>
       <c r="R16" t="n">
-        <v>6614911</v>
+        <v>6614737</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2369,12 +2369,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2401,10 +2401,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122440085</v>
+        <v>122440097</v>
       </c>
       <c r="B17" t="n">
-        <v>56290</v>
+        <v>56283</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2417,26 +2417,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100092</v>
+        <v>205992</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2663,10 +2663,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122440071</v>
+        <v>122440085</v>
       </c>
       <c r="B19" t="n">
-        <v>56297</v>
+        <v>56290</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2675,30 +2675,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>206002</v>
+        <v>100092</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2794,10 +2794,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122440103</v>
+        <v>122440078</v>
       </c>
       <c r="B20" t="n">
-        <v>56276</v>
+        <v>56295</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2806,30 +2806,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2925,10 +2925,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122440097</v>
+        <v>122440071</v>
       </c>
       <c r="B21" t="n">
-        <v>56283</v>
+        <v>56297</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2937,25 +2937,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>205992</v>
+        <v>206002</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3056,7 +3056,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122440106</v>
+        <v>122440103</v>
       </c>
       <c r="B22" t="n">
         <v>56276</v>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3115,10 +3115,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>666883</v>
+        <v>666884</v>
       </c>
       <c r="R22" t="n">
-        <v>6614610</v>
+        <v>6614611</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3145,22 +3145,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3187,10 +3187,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122440078</v>
+        <v>122440106</v>
       </c>
       <c r="B23" t="n">
-        <v>56295</v>
+        <v>56276</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3199,30 +3199,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>666884</v>
+        <v>666883</v>
       </c>
       <c r="R23" t="n">
-        <v>6614611</v>
+        <v>6614610</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3276,22 +3276,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -2071,10 +2071,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122357198</v>
+        <v>122357133</v>
       </c>
       <c r="B14" t="n">
-        <v>58089</v>
+        <v>56836</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2083,30 +2083,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103055</v>
+        <v>102954</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>666822</v>
+        <v>666888</v>
       </c>
       <c r="R14" t="n">
-        <v>6614911</v>
+        <v>6614627</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122357133</v>
+        <v>122357198</v>
       </c>
       <c r="B15" t="n">
-        <v>56836</v>
+        <v>58089</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2193,30 +2193,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102954</v>
+        <v>103055</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -2229,10 +2229,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>666888</v>
+        <v>666822</v>
       </c>
       <c r="R15" t="n">
-        <v>6614627</v>
+        <v>6614911</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -2663,10 +2663,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122440085</v>
+        <v>122440078</v>
       </c>
       <c r="B19" t="n">
-        <v>56290</v>
+        <v>56295</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2679,26 +2679,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2794,10 +2794,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122440078</v>
+        <v>122440085</v>
       </c>
       <c r="B20" t="n">
-        <v>56295</v>
+        <v>56290</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2810,26 +2810,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -2663,10 +2663,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122440078</v>
+        <v>122440085</v>
       </c>
       <c r="B19" t="n">
-        <v>56295</v>
+        <v>56290</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2679,26 +2679,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205995</v>
+        <v>100092</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2794,10 +2794,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122440085</v>
+        <v>122440078</v>
       </c>
       <c r="B20" t="n">
-        <v>56290</v>
+        <v>56295</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2810,26 +2810,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -2401,7 +2401,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122440085</v>
+        <v>122440088</v>
       </c>
       <c r="B17" t="n">
         <v>56384</v>
@@ -2436,7 +2436,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2460,10 +2460,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>666884</v>
+        <v>666883</v>
       </c>
       <c r="R17" t="n">
-        <v>6614611</v>
+        <v>6614610</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2490,22 +2490,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
+          <t>2024-06-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-06-26</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>05:30</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2532,10 +2532,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122440106</v>
+        <v>122440081</v>
       </c>
       <c r="B18" t="n">
-        <v>56370</v>
+        <v>56389</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2544,30 +2544,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2663,10 +2663,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122440097</v>
+        <v>122440085</v>
       </c>
       <c r="B19" t="n">
-        <v>56377</v>
+        <v>56384</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2679,26 +2679,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>205992</v>
+        <v>100092</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2794,10 +2794,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122440088</v>
+        <v>122440106</v>
       </c>
       <c r="B20" t="n">
-        <v>56384</v>
+        <v>56370</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2806,30 +2806,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100092</v>
+        <v>205998</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2925,10 +2925,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122440081</v>
+        <v>122440103</v>
       </c>
       <c r="B21" t="n">
-        <v>56389</v>
+        <v>56370</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2937,30 +2937,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>205995</v>
+        <v>205998</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2984,10 +2984,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>666883</v>
+        <v>666884</v>
       </c>
       <c r="R21" t="n">
-        <v>6614610</v>
+        <v>6614611</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
+          <t>2024-08-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>21:45</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3056,10 +3056,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122440103</v>
+        <v>122440078</v>
       </c>
       <c r="B22" t="n">
-        <v>56370</v>
+        <v>56389</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3068,30 +3068,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>205998</v>
+        <v>205995</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3318,10 +3318,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122440078</v>
+        <v>122440097</v>
       </c>
       <c r="B24" t="n">
-        <v>56389</v>
+        <v>56377</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3334,21 +3334,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>205995</v>
+        <v>205992</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116376087</v>
+        <v>122356817</v>
       </c>
       <c r="B2" t="n">
-        <v>100017</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Arlanda BÖP, Upl</t>
+          <t>Arlanda, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>666818</v>
+        <v>666882</v>
       </c>
       <c r="R2" t="n">
-        <v>6614563</v>
+        <v>6614737</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +748,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,27 +768,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
+          <t>Flor Rhebergen</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116376086</v>
+        <v>122440085</v>
       </c>
       <c r="B3" t="n">
-        <v>5185</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +791,56 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>105930</v>
+        <v>100092</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Arlanda BÖP, Upl</t>
+          <t>Arlanda flygplats, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>666801</v>
+        <v>666884</v>
       </c>
       <c r="R3" t="n">
-        <v>6614662</v>
+        <v>6614611</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,17 +864,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>20:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Gnag på död gran. Låga. Tror angreppet var när stammen stod upp.</t>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,27 +894,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Torge Gerwin</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
+          <t>Jacqueline Nelms, Torge Gerwin, Emily Macgregor</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116376085</v>
+        <v>122440088</v>
       </c>
       <c r="B4" t="n">
-        <v>4769</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56830</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,37 +917,56 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102306</v>
+        <v>100092</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granbarkgnagare</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Microbregma emarginatum</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Duftschmid, 1825)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Arlanda BÖP, Upl</t>
+          <t>Arlanda flygplats, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>666802</v>
+        <v>666883</v>
       </c>
       <c r="R4" t="n">
-        <v>6614665</v>
+        <v>6614610</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -954,17 +990,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>21:45</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Enstaka små cirkelrunda kläckhål i levande äldre gran.</t>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>04:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,27 +1020,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Torge Gerwin</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
+          <t>Jacqueline Nelms, Torge Gerwin, Emily Macgregor</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116376103</v>
+        <v>121622328</v>
       </c>
       <c r="B5" t="n">
-        <v>8403</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,37 +1043,56 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106554</v>
+        <v>100141</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Arlanda BÖP, Upl</t>
+          <t>Arlanda, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>666861</v>
+        <v>666894</v>
       </c>
       <c r="R5" t="n">
-        <v>6614717</v>
+        <v>6614616</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1061,12 +1116,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>23:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,27 +1146,26 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Elin Lönnberg</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr"/>
+          <t>Vide Ohlin</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>ASC0019g Groddjursinventering Arlanda</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116376106</v>
+        <v>121622330</v>
       </c>
       <c r="B6" t="n">
-        <v>56732</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1109,37 +1173,51 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102954</v>
+        <v>100141</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Laurenti, 1768)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Arlanda BÖP, Upl</t>
+          <t>Arlanda, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>666772</v>
+        <v>666912</v>
       </c>
       <c r="R6" t="n">
-        <v>6614551</v>
+        <v>6614778</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1163,17 +1241,27 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>22:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-04-11</t>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>22:23</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Läte lång stund och såg fågeln flyga över fuktäng/lågpunkt i gammal jordtäkt</t>
+          <t>Subadult möjligen hona. I liten pöl 3×3m. max 30 cm djup. Rätt igenvuxen av gräs och salix. .</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1188,27 +1276,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Mika Thunell</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna Koffman</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Vide Ohlin</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>ASC0019g Groddjursinventering Arlanda</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121622333</v>
+        <v>121622332</v>
       </c>
       <c r="B7" t="n">
-        <v>58232</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1216,26 +1303,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>208242</v>
+        <v>100141</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Större vattensalamander</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Triturus cristatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Laurenti, 1768)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1243,6 +1330,16 @@
           <t>adult</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1254,10 +1351,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>666896</v>
+        <v>666891</v>
       </c>
       <c r="R7" t="n">
-        <v>6614615</v>
+        <v>6614631</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1289,7 +1386,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>22:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1299,7 +1396,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>22:02</t>
+          <t>22:06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>satt med huvudet upp över ytan.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,12 +1435,7 @@
         <v>121622334</v>
       </c>
       <c r="B8" t="n">
-        <v>58235</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58829</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1465,15 +1562,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121622328</v>
+        <v>115808158</v>
       </c>
       <c r="B9" t="n">
-        <v>58235</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1481,56 +1573,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100141</v>
+        <v>102185</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Aromia moschata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Arlanda, Upl</t>
+          <t>Klotskogen, Klotskogen, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>666894</v>
+        <v>666909</v>
       </c>
       <c r="R9" t="n">
-        <v>6614616</v>
+        <v>6614560</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1554,22 +1627,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>23:00</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>23:00</t>
+          <t>2024-04-09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1584,31 +1647,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Magnus Stenmark</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Vide Ohlin</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>ASC0019g Groddjursinventering Arlanda</t>
-        </is>
-      </c>
+          <t>Magnus Stenmark</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121622332</v>
+        <v>116376085</v>
       </c>
       <c r="B10" t="n">
-        <v>58235</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1616,61 +1670,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100141</v>
+        <v>102306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Större vattensalamander</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Triturus cristatus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Laurenti, 1768)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>i vatten/simmande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Arlanda, Upl</t>
+          <t>Arlanda BÖP, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>666891</v>
+        <v>666802</v>
       </c>
       <c r="R10" t="n">
-        <v>6614631</v>
+        <v>6614665</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1694,27 +1724,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>22:06</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-03</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>22:06</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>satt med huvudet upp över ytan.</t>
+          <t>Enstaka små cirkelrunda kläckhål i levande äldre gran.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1729,31 +1749,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Mika Thunell</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Vide Ohlin</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>ASC0019g Groddjursinventering Arlanda</t>
-        </is>
-      </c>
+          <t>Anna Koffman</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122357299</v>
+        <v>116376102</v>
       </c>
       <c r="B11" t="n">
-        <v>57754</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4781</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1761,45 +1772,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>102306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Granbarkgnagare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Microbregma emarginatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>(Duftschmid, 1825)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Arlanda, Upl</t>
+          <t>Arlanda BÖP, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>666863</v>
+        <v>666772</v>
       </c>
       <c r="R11" t="n">
-        <v>6614722</v>
+        <v>6614596</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1823,12 +1826,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,31 +1846,26 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Flor Rhebergen</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122357200</v>
+        <v>116376106</v>
       </c>
       <c r="B12" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57364</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1889,23 +1887,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Arlanda, Upl</t>
+          <t>Arlanda BÖP, Upl</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>666857</v>
+        <v>666772</v>
       </c>
       <c r="R12" t="n">
-        <v>6614899</v>
+        <v>6614551</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1929,12 +1923,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Läte lång stund och såg fågeln flyga över fuktäng/lågpunkt i gammal jordtäkt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1949,44 +1948,39 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Petter Andersson</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Flor Rhebergen</t>
+          <t>Anna Koffman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122356806</v>
+        <v>122357133</v>
       </c>
       <c r="B13" t="n">
-        <v>57754</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57364</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103015</v>
+        <v>102954</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2009,10 +2003,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>666810</v>
+        <v>666888</v>
       </c>
       <c r="R13" t="n">
-        <v>6614633</v>
+        <v>6614627</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2039,12 +2033,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2071,19 +2065,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122357133</v>
+        <v>122357200</v>
       </c>
       <c r="B14" t="n">
-        <v>56836</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57364</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2104,11 +2093,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
@@ -2119,10 +2104,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>666888</v>
+        <v>666857</v>
       </c>
       <c r="R14" t="n">
-        <v>6614627</v>
+        <v>6614899</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2181,15 +2166,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122357198</v>
+        <v>122356854</v>
       </c>
       <c r="B15" t="n">
-        <v>58089</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58541</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2197,16 +2177,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103055</v>
+        <v>102987</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2214,11 +2194,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
@@ -2229,10 +2205,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>666822</v>
+        <v>666824</v>
       </c>
       <c r="R15" t="n">
-        <v>6614911</v>
+        <v>6615014</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2259,12 +2235,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-04-29</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,15 +2267,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122356817</v>
+        <v>122356841</v>
       </c>
       <c r="B16" t="n">
-        <v>57400</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2307,16 +2278,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>102990</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -2324,11 +2295,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
@@ -2339,10 +2306,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>666882</v>
+        <v>666879</v>
       </c>
       <c r="R16" t="n">
-        <v>6614737</v>
+        <v>6614760</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2401,37 +2368,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122440088</v>
+        <v>122357201</v>
       </c>
       <c r="B17" t="n">
-        <v>56384</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100092</v>
+        <v>102990</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2439,31 +2401,20 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Arlanda flygplats, Upl</t>
+          <t>Arlanda, Upl</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>666883</v>
+        <v>666836</v>
       </c>
       <c r="R17" t="n">
-        <v>6614610</v>
+        <v>6614862</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2490,22 +2441,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>21:45</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>04:00</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2520,81 +2461,61 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Torge Gerwin</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Jacqueline Nelms, Torge Gerwin, Emily Macgregor</t>
+          <t>Flor Rhebergen</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122440081</v>
+        <v>122357309</v>
       </c>
       <c r="B18" t="n">
-        <v>56389</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>205995</v>
+        <v>102990</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Arlanda flygplats, Upl</t>
+          <t>Arlanda, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>666883</v>
+        <v>666896</v>
       </c>
       <c r="R18" t="n">
-        <v>6614610</v>
+        <v>6614782</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2621,22 +2542,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>21:45</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>04:00</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2651,27 +2562,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Torge Gerwin</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jacqueline Nelms, Torge Gerwin, Emily Macgregor</t>
+          <t>Flor Rhebergen</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122440085</v>
+        <v>122356806</v>
       </c>
       <c r="B19" t="n">
-        <v>56384</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2679,53 +2585,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100092</v>
+        <v>103015</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Arlanda flygplats, Upl</t>
+          <t>Arlanda, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>666884</v>
+        <v>666810</v>
       </c>
       <c r="R19" t="n">
-        <v>6614611</v>
+        <v>6614633</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2752,22 +2647,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>20:15</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>05:30</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2782,81 +2667,61 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Torge Gerwin</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jacqueline Nelms, Torge Gerwin, Emily Macgregor</t>
+          <t>Flor Rhebergen</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122440106</v>
+        <v>122356816</v>
       </c>
       <c r="B20" t="n">
-        <v>56370</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>205998</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Arlanda flygplats, Upl</t>
+          <t>Arlanda, Upl</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>666883</v>
+        <v>666934</v>
       </c>
       <c r="R20" t="n">
-        <v>6614610</v>
+        <v>6614672</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2883,22 +2748,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-06-24</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>21:45</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-06-26</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>04:00</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2913,81 +2768,65 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Torge Gerwin</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Jacqueline Nelms, Torge Gerwin, Emily Macgregor</t>
+          <t>Flor Rhebergen</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122440103</v>
+        <v>122357145</v>
       </c>
       <c r="B21" t="n">
-        <v>56370</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>205998</v>
+        <v>103015</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Arlanda flygplats, Upl</t>
+          <t>Arlanda, Upl</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>666884</v>
+        <v>666945</v>
       </c>
       <c r="R21" t="n">
-        <v>6614611</v>
+        <v>6614675</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3014,22 +2853,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>20:15</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>05:30</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3044,27 +2873,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Torge Gerwin</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Jacqueline Nelms, Torge Gerwin, Emily Macgregor</t>
+          <t>Flor Rhebergen</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122440078</v>
+        <v>122357299</v>
       </c>
       <c r="B22" t="n">
-        <v>56389</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3072,53 +2896,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>205995</v>
+        <v>103015</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Arlanda flygplats, Upl</t>
+          <t>Arlanda, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>666884</v>
+        <v>666863</v>
       </c>
       <c r="R22" t="n">
-        <v>6614611</v>
+        <v>6614722</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3145,22 +2958,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>20:15</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>05:30</t>
+          <t>2024-04-08</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3175,81 +2978,65 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Torge Gerwin</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Jacqueline Nelms, Torge Gerwin, Emily Macgregor</t>
+          <t>Flor Rhebergen</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122440071</v>
+        <v>122357140</v>
       </c>
       <c r="B23" t="n">
-        <v>56391</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58439</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>206002</v>
+        <v>103018</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Arlanda flygplats, Upl</t>
+          <t>Arlanda, Upl</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>666884</v>
+        <v>666945</v>
       </c>
       <c r="R23" t="n">
-        <v>6614611</v>
+        <v>6614731</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3276,22 +3063,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>20:15</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>05:30</t>
+          <t>2024-04-29</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3306,81 +3083,61 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Torge Gerwin</t>
+          <t>Petter Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Jacqueline Nelms, Torge Gerwin, Emily Macgregor</t>
+          <t>Flor Rhebergen</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122440097</v>
+        <v>122356840</v>
       </c>
       <c r="B24" t="n">
-        <v>56377</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>205992</v>
+        <v>103021</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>autobox med tidsexpansion</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Arlanda flygplats, Upl</t>
+          <t>Arlanda, Upl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>666884</v>
+        <v>666878</v>
       </c>
       <c r="R24" t="n">
-        <v>6614611</v>
+        <v>6614786</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3407,22 +3164,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-08-13</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>20:15</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>05:30</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3437,15 +3184,1954 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>122357146</v>
+      </c>
+      <c r="B25" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>666938</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6614705</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>122357297</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>666843</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6614762</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-04-08</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>122356848</v>
+      </c>
+      <c r="B27" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>666910</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6614761</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>122357132</v>
+      </c>
+      <c r="B28" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>666918</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6614634</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>122357143</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>666930</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6614660</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>122357198</v>
+      </c>
+      <c r="B30" t="n">
+        <v>58676</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>103055</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Gulsparv</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Emberiza citrinella</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>666822</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6614911</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-04-29</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Petter Andersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Flor Rhebergen</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>116376086</v>
+      </c>
+      <c r="B31" t="n">
+        <v>5199</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>105930</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Vågbandad barkbock</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Arlanda BÖP, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>666801</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6614662</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Gnag på död gran. Låga. Tror angreppet var när stammen stod upp.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anna Koffman</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>116376103</v>
+      </c>
+      <c r="B32" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Arlanda BÖP, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>666861</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6614717</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Elin Lönnberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>122440097</v>
+      </c>
+      <c r="B33" t="n">
+        <v>56823</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>205992</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Vattenfladdermus</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Myotis daubentonii</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Kuhl, 1817)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Arlanda flygplats, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>666884</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6614611</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
           <t>Torge Gerwin</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
+      <c r="AX33" t="inlineStr">
         <is>
           <t>Jacqueline Nelms, Torge Gerwin, Emily Macgregor</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>122440078</v>
+      </c>
+      <c r="B34" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Arlanda flygplats, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>666884</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6614611</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Torge Gerwin</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jacqueline Nelms, Torge Gerwin, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>122440081</v>
+      </c>
+      <c r="B35" t="n">
+        <v>56835</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Arlanda flygplats, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>666883</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6614610</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Torge Gerwin</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jacqueline Nelms, Torge Gerwin, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>122440103</v>
+      </c>
+      <c r="B36" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Arlanda flygplats, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>666884</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6614611</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Torge Gerwin</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jacqueline Nelms, Torge Gerwin, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>122440106</v>
+      </c>
+      <c r="B37" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Arlanda flygplats, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>666883</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6614610</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-06-24</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>21:45</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-06-26</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>04:00</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Torge Gerwin</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jacqueline Nelms, Torge Gerwin, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>122440071</v>
+      </c>
+      <c r="B38" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>autobox med tidsexpansion</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Arlanda flygplats, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>666884</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6614611</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-08-13</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Torge Gerwin</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jacqueline Nelms, Torge Gerwin, Emily Macgregor</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>121622333</v>
+      </c>
+      <c r="B39" t="n">
+        <v>58826</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>208242</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lissotriton vulgaris</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>666896</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6614615</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>22:02</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>22:02</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Vide Ohlin</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>ASC0019g Groddjursinventering Arlanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>121622331</v>
+      </c>
+      <c r="B40" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Arlanda, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>666849</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6614748</v>
+      </c>
+      <c r="S40" t="n">
+        <v>5</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>22:23</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-05-03</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>22:23</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>spelande hanar sågs och hördes i stort dike.</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Mika Thunell</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Vide Ohlin</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>ASC0019g Groddjursinventering Arlanda</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>116376087</v>
+      </c>
+      <c r="B41" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Arlanda BÖP, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>666818</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6614563</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sigtuna</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lunda</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-04-11</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Arvid de Jong</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Anna Koffman</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 61919-2021 artfynd.xlsx
+++ b/artfynd/A 61919-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY41"/>
+  <dimension ref="A1:AZ41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122356817</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122440085</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1029,6 +1044,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122440088</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1159,6 +1179,11 @@
           <t>ASC0019g Groddjursinventering Arlanda</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121622328</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1289,6 +1314,11 @@
           <t>ASC0019g Groddjursinventering Arlanda</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121622330</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1429,6 +1459,11 @@
           <t>ASC0019g Groddjursinventering Arlanda</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121622332</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1559,6 +1594,11 @@
           <t>ASC0019g Groddjursinventering Arlanda</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121622334</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1656,6 +1696,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115808158</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1758,6 +1803,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116376085</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1855,6 +1905,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116376102</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1957,6 +2012,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116376106</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2062,6 +2122,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122357133</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2163,6 +2228,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122357200</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2264,6 +2334,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122356854</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2365,6 +2440,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122356841</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2470,6 +2550,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122357201</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2571,6 +2656,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122357309</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2676,6 +2766,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122356806</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2777,6 +2872,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122356816</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2882,6 +2982,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122357145</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2987,6 +3092,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122357299</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3092,6 +3202,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122357140</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3193,6 +3308,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122356840</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3298,6 +3418,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122357146</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3399,6 +3524,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122357297</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3500,6 +3630,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122356848</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3605,6 +3740,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122357132</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3710,6 +3850,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122357143</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3815,6 +3960,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122357198</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3917,6 +4067,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116376086</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4014,6 +4169,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116376103</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4140,6 +4300,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122440097</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4266,6 +4431,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122440078</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4392,6 +4562,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122440081</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4518,6 +4693,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122440103</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4644,6 +4824,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122440106</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4770,6 +4955,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122440071</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4895,6 +5085,11 @@
           <t>ASC0019g Groddjursinventering Arlanda</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121622333</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5035,6 +5230,11 @@
           <t>ASC0019g Groddjursinventering Arlanda</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121622331</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5132,8 +5332,55 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116376087</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>